--- a/insurance_forms/021_life_insurance_discharge_form--insurance_forms.xlsx
+++ b/insurance_forms/021_life_insurance_discharge_form--insurance_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>policy_holder_phone</t>
+          <t>policy_holder_phone_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Policy Holder Phone</t>
+          <t>Policy Holder Phone 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>policy_holder_address</t>
+          <t>policy_holder_address_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Policy Holder Address</t>
+          <t>Policy Holder Address 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>policy_holder_title</t>
+          <t>policy_holder_title_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Policy Holder Title</t>
+          <t>Policy Holder Title 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'beneficiary'}</t>
+          <t>beneficiary</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'Beneficiary'}</t>
+          <t>Beneficiary</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'claimant'}</t>
+          <t>claimant</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'Claimant'}</t>
+          <t>Claimant</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'policy_holder'}</t>
+          <t>policy_holder</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Policy Holder'}</t>
+          <t>Policy Holder</t>
         </is>
       </c>
     </row>
